--- a/2. Proyectos/1. Interpreta Chile/01 Meta - Proyectos/facebook scraper/url/URL_POST.xlsx
+++ b/2. Proyectos/1. Interpreta Chile/01 Meta - Proyectos/facebook scraper/url/URL_POST.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Jose Ordinola - Vault Projects\2. Proyectos\1. Interpreta Chile\01 Meta - Proyectos\facebook scraper\url\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/josealonsoordinolaaucca/Documents/Documentos/Vault/Vault/2. Proyectos/1. Interpreta Chile/01 Meta - Proyectos/facebook scraper/url/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{198ECCD9-AA1E-4291-B734-EB39A9227061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9125ED45-D121-4B45-ABB5-114532CC8545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5655" yWindow="3705" windowWidth="28800" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14480" yWindow="660" windowWidth="14180" windowHeight="15940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,79 +20,388 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="125">
   <si>
     <t>url_facebook</t>
   </si>
   <si>
-    <t>https://www.facebook.com/share/v/19YFHGaUi6/</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/share/p/15eVhmd6cz/</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/share/p/16VZwYj3uG/</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/share/v/16M1Fx65pG/</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/share/p/1QRFi7eTWr/</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/share/p/1Bs9YR9cgb/</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/share/p/1Ybj85WZt4/</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/share/p/1DyzbpyJHK/</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/share/p/1DxJzJsUqK/</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/share/p/1HhC8bgGbU/</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/share/v/12M4kTEPKhf/</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/share/p/16bhAFdgkL/</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/share/p/16LULnBukq/</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/share/p/1AarMjN3em/</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/share/p/1CCmrsaVom/</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/share/p/1AKy4mPbWQ/</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/share/1B6imercs4/?mibextid=WC7FNe</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/share/p/19qVkzJTsE/</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/share/v/1EkbjEJcYe/</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/share/p/16SAbb7Uxi/</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/share/v/1AojFKSKyQ/</t>
+    <t>https://www.facebook.com/881095048648989/posts/1328179165322947</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/881095048648989/posts/1325830758891121</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/203788766452764/posts/1362289518600161</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/203788766452764/posts/1361553808673732</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/203788766452764/posts/1361413442021102</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/203788766452764/posts/1360802758748837</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/203788766452764/posts/1360470148782098</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/203788766452764/posts/1360085705487209</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/203788766452764/posts/1359811752181271</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/203788766452764/posts/1359221462240300</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/203788766452764/posts/1359054368923676</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/203788766452764/posts/1358875345608245</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/203788766452764/posts/1358390442323402</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/203788766452764/posts/1358265315669248</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/787786953813702</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/729672499824517</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/636315485698560</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1353656323199590</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1302718061243190</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1302708167910846</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1302706011244395</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1302705897911073</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1302705751244421</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1302703764577953</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1302703341244662</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1302703111244685</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1302694614578868</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1302693584578971</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1302591461255850</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1302589511256045</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1302589364589393</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1302589167922746</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1302589114589418</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1302588511256145</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1302413821273614</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1302041967977466</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1302036774644652</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1302030994645230</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1302014997980163</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301964847985178</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301959284652401</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301954531319543</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301945174653812</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301943537987309</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301941327987530</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301925267989136</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301921427989520</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301921344656195</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301919424656387</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301902724658057</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301898747991788</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301889711326025</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301887594659570</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301887561326240</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301887067992956</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301884531326543</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301883831326613</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301881901326806</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301866314661698</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301849494663380</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301837457997917</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301835654664764</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301835611331435</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301834994664830</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301834287998234</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301833701331626</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301832911331705</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301832377998425</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301831951331801</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301829674665362</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301815901333406</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301772008004462</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301228264725503</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301203824727947</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301183631396633</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301177191397277</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301177034730626</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301167498064913</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301163754731954</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301152938066369</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301130048068658</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301129178068745</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1301126231402373</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1300886451426351</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1300860254762304</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1300856198096043</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1300855491429447</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1300704861444510</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1300497961465200</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1300479124800417</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1300444548137208</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1300430681471928</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1300400961474900</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1300398171475179</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1300375061477490</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1300350988146564</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1300350021479994</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1300349898146673</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1300349791480017</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1300344281480568</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1300341871480809</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1300336628148000</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1300330601481936</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1300329911482005</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1300325381482458</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1300250858156577</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1300158401499156</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1300134714834858</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1300134514834878</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1300134418168221</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1300105661504430</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1300099381505058</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1266747118161274</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/202946623111323/posts/1262106925404537</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/125532598842535/posts/1374013318066183</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/125532598842535/posts/1373788404755341</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/125532598842535/posts/1373167591484089</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/125532598842535/posts/1373021314832050</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/125532598842535/posts/1372953431505505</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/125532598842535/posts/1372075174926664</t>
+  </si>
+  <si>
+    <t>JeannetteJaraRoman</t>
+  </si>
+  <si>
+    <t>parisioficial</t>
+  </si>
+  <si>
+    <t>joseantoniokast</t>
+  </si>
+  <si>
+    <t>evelynmatthei</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -104,6 +413,15 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -138,19 +456,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -451,123 +769,978 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="76.28515625" style="2" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:B121"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="B3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="B4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="B5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="B6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="B7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="B8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="B9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="B10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="B11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="B12" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="B13" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="B14" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="B15" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="B16" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="B17" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="B18" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="B19" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="B20" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="B21" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
         <v>21</v>
       </c>
+      <c r="B22" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>111</v>
+      </c>
+      <c r="B112" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>112</v>
+      </c>
+      <c r="B113" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>113</v>
+      </c>
+      <c r="B114" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>114</v>
+      </c>
+      <c r="B115" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>115</v>
+      </c>
+      <c r="B116" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>116</v>
+      </c>
+      <c r="B117" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>117</v>
+      </c>
+      <c r="B118" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>118</v>
+      </c>
+      <c r="B119" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>119</v>
+      </c>
+      <c r="B120" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>120</v>
+      </c>
+      <c r="B121" t="s">
+        <v>121</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A3" r:id="rId1" xr:uid="{C6DAB1DC-2396-2C49-8E91-5D73835F589F}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>